--- a/budget-transfer/process/11-checklist-01-readiness.xlsx
+++ b/budget-transfer/process/11-checklist-01-readiness.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/budget-transfer/process/11-checklist-01-readiness.xlsx
+++ b/budget-transfer/process/11-checklist-01-readiness.xlsx
@@ -19,8 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -707,7 +708,7 @@
       </c>
       <c r="B4" s="25" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
@@ -743,7 +744,7 @@
       </c>
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -755,7 +756,7 @@
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>IT予算移管 憲章（BTR-R-02）、Runbook（BTR-P-08-01 進行役編・08-04 案件担当編）</t>
+          <t>IT予算移管 憲章（BTR-R-02）、Runbook（BTR-P-08-01 事務局編・08-04 窓口担当編）</t>
         </is>
       </c>
     </row>
@@ -781,14 +782,14 @@
     <row r="12" ht="30" customHeight="1" s="22">
       <c r="A12" s="46" t="inlineStr">
         <is>
-          <t>移管ステータスが「合意済み」の案件について、合意済みになったら、引継ぎに合わせて確認する（Runbook 案件担当編 §3.8）。判定が「完了」になったら、移管ステータスを「準備完了」にする。</t>
+          <t>移管ステータスが「合意済み」の案件について、合意済みになったら、引継ぎに合わせて確認する（Runbook 窓口担当編 §3.8）。判定が「完了」になったら、移管ステータスを「準備完了」にする。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" s="22">
       <c r="A13" s="46" t="inlineStr">
         <is>
-          <t>結果が NG の項目は「NGのときの対応」に従う。判断が要る状況は、この表で判定せず、Runbook 案件担当編 §4 の例外対応へ回す。</t>
+          <t>結果が NG の項目は「NGのときの対応」に従う。判断が要る状況は、この表で判定せず、Runbook 窓口担当編 §4 の例外対応へ回す。</t>
         </is>
       </c>
     </row>
@@ -958,12 +959,12 @@
       </c>
       <c r="E4" s="35" t="inlineStr">
         <is>
-          <t>憲章 第10条、Runbook 案件担当編 §3.5</t>
+          <t>憲章 第10条、Runbook 窓口担当編 §3.5</t>
         </is>
       </c>
       <c r="F4" s="35" t="inlineStr">
         <is>
-          <t>案件担当が Runbook 案件担当編 §3.4・§3.5 を行う</t>
+          <t>窓口担当が Runbook 窓口担当編 §3.4・§3.5 を行う</t>
         </is>
       </c>
     </row>
@@ -983,17 +984,17 @@
       </c>
       <c r="D5" s="35" t="inlineStr">
         <is>
-          <t>予算移管シート「業務」で業務区分が間接業務の業務と、引継ぎ要領（Runbook 案件担当編 付録）の受け手、「進捗」の C-07 を突き合わせる</t>
+          <t>予算移管シート「業務」で業務区分が間接業務の業務と、引継ぎ要領（Runbook 窓口担当編 付録）の受け手、「進捗」の C-07 を突き合わせる</t>
         </is>
       </c>
       <c r="E5" s="35" t="inlineStr">
         <is>
-          <t>憲章 第10条、Runbook 案件担当編 §3.7</t>
+          <t>憲章 第10条、Runbook 窓口担当編 §3.7</t>
         </is>
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>案件担当が引継ぎを行う（案件担当編 §3.7）。引継ぎ要領に足りないことがあれば、進行役が付録を改める（進行役編 §3.3）</t>
+          <t>窓口担当が引継ぎを行う（窓口担当編 §3.7）。引継ぎ要領に足りないことがあれば、事務局が付録を改める（事務局編 §3.3）</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1024,7 @@
       </c>
       <c r="F6" s="35" t="inlineStr">
         <is>
-          <t>案件担当が移管対象部門の担当者と調整して、IT部門側の手順の改定を含めて手続きを起票し、完了予定を記入する（案件担当編 §3.4・§3.7）。起票できなければ、その業務は今の担当のまま行うことを合意文書に書き、案件担当編 §4 へ</t>
+          <t>窓口担当が移管対象部門の担当者と調整して、IT部門側の手順の改定を含めて手続きを起票し、完了予定を記入する（窓口担当編 §3.4・§3.7）。起票できなければ、その業務は今の担当のまま行うことを合意文書に書き、窓口担当編 §4 へ</t>
         </is>
       </c>
     </row>
@@ -1901,10 +1902,24 @@
       <c r="E7" s="35" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="22">
-      <c r="A8" s="35" t="n"/>
-      <c r="B8" s="35" t="n"/>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B8" s="55" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C8" s="54" t="inlineStr">
+        <is>
+          <t>IT予算移管ガイドラインに合わせ、進行役を事務局、案件担当を窓口担当に改めた</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>予算移管事務局</t>
+        </is>
+      </c>
       <c r="E8" s="35" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="22">
